--- a/preview/pr-13/CodeSystem-dem-geschlecht.xlsx
+++ b/preview/pr-13/CodeSystem-dem-geschlecht.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T07:34:58+00:00</t>
+    <t>2026-09-30T07:33:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -141,31 +141,31 @@
     <t>weiblich</t>
   </si>
   <si>
-    <t>Weiblich</t>
+    <t>Female</t>
   </si>
   <si>
     <t>maennlich</t>
   </si>
   <si>
-    <t>Männlich</t>
+    <t>Male</t>
   </si>
   <si>
     <t>nicht-binaer</t>
   </si>
   <si>
-    <t>Nicht-binär</t>
+    <t>Non-binary</t>
   </si>
   <si>
     <t>andere</t>
   </si>
   <si>
-    <t>Andere</t>
+    <t>Other</t>
   </si>
   <si>
     <t>keine-angabe</t>
   </si>
   <si>
-    <t>Möchte ich nicht sagen</t>
+    <t>Prefer not to say</t>
   </si>
 </sst>
 </file>

--- a/preview/pr-13/CodeSystem-dem-geschlecht.xlsx
+++ b/preview/pr-13/CodeSystem-dem-geschlecht.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T07:33:31+00:00</t>
+    <t>2026-09-30T08:17:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/preview/pr-13/CodeSystem-dem-geschlecht.xlsx
+++ b/preview/pr-13/CodeSystem-dem-geschlecht.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T08:17:00+00:00</t>
+    <t>2026-09-30T08:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
